--- a/artfynd/A 74364-2021 artfynd.xlsx
+++ b/artfynd/A 74364-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 74364-2021 artfynd.xlsx
+++ b/artfynd/A 74364-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84164460</v>
+        <v>84164463</v>
       </c>
       <c r="B3" t="n">
-        <v>95511</v>
+        <v>5113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>678370.3966166389</v>
+        <v>678368.2294654303</v>
       </c>
       <c r="R3" t="n">
-        <v>6686352.74314291</v>
+        <v>6686346.177807153</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>84164463</v>
+        <v>96925797</v>
       </c>
       <c r="B4" t="n">
-        <v>5113</v>
+        <v>108194</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,34 +916,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>219711</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ytternuttö, Upl</t>
+          <t>Rörmar, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>678368.2294654303</v>
+        <v>678438.0269986434</v>
       </c>
       <c r="R4" t="n">
-        <v>6686346.177807153</v>
+        <v>6686384.374922391</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,7 +970,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1000,19 +1000,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tore Dahlberg, Karl Soler Kinnerbäck</t>
+          <t>Karin Wiklund, Johan Lilja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96925797</v>
+        <v>97070729</v>
       </c>
       <c r="B5" t="n">
         <v>108194</v>
@@ -1046,19 +1046,23 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rörmar, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>678438.0269986434</v>
+        <v>678440.9574445606</v>
       </c>
       <c r="R5" t="n">
-        <v>6686384.374922391</v>
+        <v>6686385.512121973</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,28 +1110,38 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karin Wiklund, Johan Lilja</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Johan Lilja, Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97070729</v>
+        <v>110781007</v>
       </c>
       <c r="B6" t="n">
-        <v>108194</v>
+        <v>96326</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,41 +1154,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rörmar, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>678440.9574445606</v>
+        <v>678452.7581761701</v>
       </c>
       <c r="R6" t="n">
-        <v>6686385.512121973</v>
+        <v>6686327.459503386</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1208,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1208,7 +1218,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1222,14 +1232,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1239,126 +1243,10 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Lilja, Karin Wiklund</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>110781007</v>
-      </c>
-      <c r="B7" t="n">
-        <v>96326</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>219798</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Epipactis helleborine</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Rörmar, Upl</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>678452.7581761701</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6686327.459503386</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Östhammar</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Börstil</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2023-07-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2023-07-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Johan Lilja</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Johan Lilja</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>

--- a/artfynd/A 74364-2021 artfynd.xlsx
+++ b/artfynd/A 74364-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84164463</v>
+        <v>84164460</v>
       </c>
       <c r="B3" t="n">
-        <v>5113</v>
+        <v>95511</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>221944</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>678368.2294654303</v>
+        <v>678370.3966166389</v>
       </c>
       <c r="R3" t="n">
-        <v>6686346.177807153</v>
+        <v>6686352.74314291</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96925797</v>
+        <v>84164463</v>
       </c>
       <c r="B4" t="n">
-        <v>108194</v>
+        <v>5113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,34 +916,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219711</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rörmar, Upl</t>
+          <t>Ytternuttö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>678438.0269986434</v>
+        <v>678368.2294654303</v>
       </c>
       <c r="R4" t="n">
-        <v>6686384.374922391</v>
+        <v>6686346.177807153</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,7 +970,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2020-04-05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1000,19 +1000,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Karin Wiklund, Johan Lilja</t>
+          <t>Ingemar Södergren, Tore Dahlberg, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97070729</v>
+        <v>96925797</v>
       </c>
       <c r="B5" t="n">
         <v>108194</v>
@@ -1046,23 +1046,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rörmar, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>678440.9574445606</v>
+        <v>678438.0269986434</v>
       </c>
       <c r="R5" t="n">
-        <v>6686385.512121973</v>
+        <v>6686384.374922391</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,38 +1106,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Lilja, Karin Wiklund</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
-        </is>
-      </c>
+          <t>Karin Wiklund, Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110781007</v>
+        <v>97070729</v>
       </c>
       <c r="B6" t="n">
-        <v>96326</v>
+        <v>108194</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,37 +1140,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rörmar, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>678452.7581761701</v>
+        <v>678440.9574445606</v>
       </c>
       <c r="R6" t="n">
-        <v>6686327.459503386</v>
+        <v>6686385.512121973</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1198,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1218,7 +1208,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1232,8 +1222,14 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1243,10 +1239,126 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
+          <t>Johan Lilja, Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110781007</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96326</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rörmar, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>678452.7581761701</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6686327.459503386</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Johan Lilja</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
